--- a/artfynd/A 25327-2026 artfynd.xlsx
+++ b/artfynd/A 25327-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134600248</v>
+        <v>134601170</v>
       </c>
       <c r="B2" t="n">
-        <v>5201</v>
+        <v>57162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,54 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörgården, Sörgården, Vg</t>
+          <t>Ekeberget, Ekeberget, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481969</v>
+        <v>481923</v>
       </c>
       <c r="R2" t="n">
-        <v>6506667</v>
+        <v>6506924</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -745,7 +765,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +775,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kläckhål och gnagspår</t>
+          <t>Färsk bälgrop med fjädrar fr  tupp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +804,118 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134600248</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sörgården, Sörgården, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>481969</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6506667</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnagspår</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25327-2026 artfynd.xlsx
+++ b/artfynd/A 25327-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134601170</v>
+        <v>134601188</v>
       </c>
       <c r="B2" t="n">
-        <v>57162</v>
+        <v>96783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,54 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ekeberget, Ekeberget, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481923</v>
+        <v>481939</v>
       </c>
       <c r="R2" t="n">
-        <v>6506924</v>
+        <v>6506914</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -765,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -775,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färsk bälgrop med fjädrar fr  tupp.</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134600248</v>
+        <v>135014158</v>
       </c>
       <c r="B3" t="n">
-        <v>5201</v>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörgården, Sörgården, Vg</t>
+          <t>Ekeberget, Ekeberget, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481969</v>
+        <v>481916</v>
       </c>
       <c r="R3" t="n">
-        <v>6506667</v>
+        <v>6506936</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -872,27 +856,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kläckhål och gnagspår</t>
+          <t>På riktigt gammal tall som slingrar sig på hällen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +900,2101 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134601018</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nedre Finnfallet, Nedre Finnfallet, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>481960</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6507043</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135013230</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>481902</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6506850</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födohack vid basen av död tall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135013751</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>481860</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6506895</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födohack i död tall.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134602280</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>481935</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6506823</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tretå ringhack äldre längre ner och massor med färska med riklig savrinning längre upp mot toppen. Grov tall.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135012844</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>481934</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6506842</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack och färska ringhack med savflöde på tall. Syns inte så bra på bilderna</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135013137</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>481918</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6506845</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134601170</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>481923</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6506924</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färsk bälgrop med fjädrar fr  tupp.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134601375</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>481957</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6506833</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt under betad tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135013516</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>481864</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6506880</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134600725</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>481851</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6506931</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135014914</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>481968</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6506795</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Och kläckhål på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135014841</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nedre Finnfallet, Nedre Finnfallet, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>481991</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6506905</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Har film på den.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135229437</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>481915</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6506892</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134600248</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sörgården, Sörgården, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>481969</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6506667</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnagspår</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134600732</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>481851</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6506928</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135014902</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>481964</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6506793</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Och kläckhål.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135014184</v>
+      </c>
+      <c r="B20" t="n">
+        <v>61527</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106670</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svart skogssnigel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Arion ater ater</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>481926</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6506933</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134600752</v>
+      </c>
+      <c r="B21" t="n">
+        <v>40305</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>481851</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6506927</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Kläckhål i levande björk med skrovelbark.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25327-2026 artfynd.xlsx
+++ b/artfynd/A 25327-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134601188</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135014158</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134601018</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135013230</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135013751</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1363,6 +1393,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602280</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,6 +1515,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135012844</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1597,6 +1637,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135013137</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1729,6 +1774,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134601170</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1846,6 +1896,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134601375</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1958,6 +2013,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135013516</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2070,6 +2130,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600725</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2187,6 +2252,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135014914</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2308,6 +2378,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135014841</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2410,6 +2485,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229437</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2528,6 +2608,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600248</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2640,6 +2725,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600732</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2757,6 +2847,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135014902</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2873,6 +2968,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135014184</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2995,8 +3095,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600752</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25327-2026 artfynd.xlsx
+++ b/artfynd/A 25327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134601188</v>
       </c>
       <c r="B2" t="n">
-        <v>96783</v>
+        <v>96827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135014158</v>
       </c>
       <c r="B3" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>134601018</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>135013230</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135013751</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>134602280</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>135012844</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>135013137</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>134601375</v>
       </c>
       <c r="B11" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135013516</v>
       </c>
       <c r="B12" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>135014841</v>
       </c>
       <c r="B15" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>135229437</v>
       </c>
       <c r="B16" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>135014184</v>
       </c>
       <c r="B20" t="n">
-        <v>61527</v>
+        <v>61536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>134600752</v>
       </c>
       <c r="B21" t="n">
-        <v>40305</v>
+        <v>40308</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 25327-2026 artfynd.xlsx
+++ b/artfynd/A 25327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134601188</v>
       </c>
       <c r="B2" t="n">
-        <v>96827</v>
+        <v>96854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135014158</v>
       </c>
       <c r="B3" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25327-2026 artfynd.xlsx
+++ b/artfynd/A 25327-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134601170</v>
+        <v>134601188</v>
       </c>
       <c r="B2" t="n">
-        <v>57162</v>
+        <v>96859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,54 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ekeberget, Ekeberget, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481923</v>
+        <v>481939</v>
       </c>
       <c r="R2" t="n">
-        <v>6506924</v>
+        <v>6506914</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -770,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -780,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:47</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färsk bälgrop med fjädrar fr  tupp.</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,13 +786,2343 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/134601188</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135014158</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>481916</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6506936</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På riktigt gammal tall som slingrar sig på hällen.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135014158</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134601018</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nedre Finnfallet, Nedre Finnfallet, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>481960</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6507043</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134601018</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135013230</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>481902</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6506850</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födohack vid basen av död tall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135013230</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135013751</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>481860</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6506895</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födohack i död tall.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135013751</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134602280</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>481935</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6506823</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tretå ringhack äldre längre ner och massor med färska med riklig savrinning längre upp mot toppen. Grov tall.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602280</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135012844</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>481934</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6506842</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack och färska ringhack med savflöde på tall. Syns inte så bra på bilderna</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135012844</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135013137</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>481918</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6506845</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135013137</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134601170</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>481923</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6506924</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färsk bälgrop med fjädrar fr  tupp.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134601170</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134601375</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>481957</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6506833</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt under betad tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134601375</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135013516</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>481864</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6506880</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135013516</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134600725</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>481851</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6506931</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600725</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135014914</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>481968</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6506795</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Och kläckhål på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135014914</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135014841</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nedre Finnfallet, Nedre Finnfallet, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>481991</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6506905</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Har film på den.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135014841</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135229437</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>481915</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6506892</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229437</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134600248</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sörgården, Sörgården, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>481969</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6506667</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnagspår</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600248</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134600732</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>481851</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6506928</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600732</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135014902</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>481964</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6506793</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Och kläckhål.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135014902</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135014184</v>
+      </c>
+      <c r="B20" t="n">
+        <v>61536</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106670</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svart skogssnigel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Arion ater ater</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>481926</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6506933</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135014184</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134600752</v>
+      </c>
+      <c r="B21" t="n">
+        <v>40308</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ekeberget, Ekeberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>481851</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6506927</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Kläckhål i levande björk med skrovelbark.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600752</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25327-2026 artfynd.xlsx
+++ b/artfynd/A 25327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134601188</v>
       </c>
       <c r="B2" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135014158</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
